--- a/engenharia/terraplanagem-u6310/IMPORTACAO_TERRAPLAN_TANQUE_Rev1-MC.xlsx
+++ b/engenharia/terraplanagem-u6310/IMPORTACAO_TERRAPLAN_TANQUE_Rev1-MC.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="PARÂMETROS" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="IMPORTAÇÃO" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="IMPORTAÇÃO " sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="CONTROLE DE REVISÃO" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -18,10 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -113,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -141,16 +142,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -516,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -727,7 +731,7 @@
       <c r="E12" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="13" t="n">
         <v>2</v>
       </c>
     </row>
@@ -751,7 +755,7 @@
       <c r="E13" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="F13" s="13" t="n">
         <v>2</v>
       </c>
     </row>
@@ -775,7 +779,7 @@
       <c r="E14" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="F14" s="13" t="n">
         <v>2</v>
       </c>
     </row>
@@ -799,7 +803,7 @@
       <c r="E15" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="F15" s="13" t="n">
         <v>2</v>
       </c>
     </row>
@@ -821,10 +825,10 @@
         <v>1756.44</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="12" t="n">
         <v>1</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
@@ -837,7 +841,35 @@
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Para o TQ-6312824 (tanque único dividido em 2 FTs), a fração é 1/2 do corte da linha.</t>
+          <t>Para o TQ-6312824 — tanque único dividido em 2 FTs — 'Tanques por FT' vale 0,5, produzindo a mesma fração de 1/2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>TOTAL DAS 10 FICHAS DE TAREFA (m³, volume solto)</t>
+        </is>
+      </c>
+      <c r="C21" s="14">
+        <f>SUM('IMPORTAÇÃO '!I2:I11)</f>
+        <v/>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Confere com o item 2 do RESUMO da memória de cálculo (24.175,07 m³).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>A aba IMPORTAÇÃO não traz linha de total, para que uma rotina que varra até a última linha preenchida não a leia como registro.</t>
         </is>
       </c>
     </row>
@@ -852,7 +884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:Y11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1035,7 +1067,7 @@
           <t>FT-CV-2619</t>
         </is>
       </c>
-      <c r="F2" s="13" t="n">
+      <c r="F2" s="16" t="n">
         <v>46262</v>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -1048,7 +1080,7 @@
           <t>U6310-C-610246000</t>
         </is>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="17">
         <f>PARÂMETROS!$C$12*(PARÂMETROS!$F$12/PARÂMETROS!$E$12)*PARÂMETROS!$C$5</f>
         <v/>
       </c>
@@ -1131,7 +1163,7 @@
           <t>FT-CV-2620</t>
         </is>
       </c>
-      <c r="F3" s="13" t="n">
+      <c r="F3" s="16" t="n">
         <v>46269</v>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1144,7 +1176,7 @@
           <t>U6310-C-610246000</t>
         </is>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="17">
         <f>PARÂMETROS!$C$12*(PARÂMETROS!$F$12/PARÂMETROS!$E$12)*PARÂMETROS!$C$5</f>
         <v/>
       </c>
@@ -1227,7 +1259,7 @@
           <t>FT-CV-2621</t>
         </is>
       </c>
-      <c r="F4" s="13" t="n">
+      <c r="F4" s="16" t="n">
         <v>46276</v>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1240,7 +1272,7 @@
           <t>U6310-C-610250000</t>
         </is>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="17">
         <f>PARÂMETROS!$C$13*(PARÂMETROS!$F$13/PARÂMETROS!$E$13)*PARÂMETROS!$C$5</f>
         <v/>
       </c>
@@ -1323,7 +1355,7 @@
           <t>FT-CV-2622</t>
         </is>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="16" t="n">
         <v>46283</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1336,7 +1368,7 @@
           <t>U6310-C-610250000</t>
         </is>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="17">
         <f>PARÂMETROS!$C$13*(PARÂMETROS!$F$13/PARÂMETROS!$E$13)*PARÂMETROS!$C$5</f>
         <v/>
       </c>
@@ -1419,7 +1451,7 @@
           <t>FT-CV-2623</t>
         </is>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="16" t="n">
         <v>46290</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -1432,7 +1464,7 @@
           <t>U6312-C-710073000</t>
         </is>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="17">
         <f>PARÂMETROS!$C$16*(PARÂMETROS!$F$16/PARÂMETROS!$E$16)*PARÂMETROS!$C$5</f>
         <v/>
       </c>
@@ -1515,7 +1547,7 @@
           <t>FT-CV-2624</t>
         </is>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="16" t="n">
         <v>46297</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1528,7 +1560,7 @@
           <t>U6312-C-710073000</t>
         </is>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="17">
         <f>PARÂMETROS!$C$16*(PARÂMETROS!$F$16/PARÂMETROS!$E$16)*PARÂMETROS!$C$5</f>
         <v/>
       </c>
@@ -1611,7 +1643,7 @@
           <t>FT-CV-2625</t>
         </is>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="16" t="n">
         <v>46304</v>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -1624,7 +1656,7 @@
           <t>U6310-C-620256000</t>
         </is>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="17">
         <f>PARÂMETROS!$C$14*(PARÂMETROS!$F$14/PARÂMETROS!$E$14)*PARÂMETROS!$C$5</f>
         <v/>
       </c>
@@ -1707,7 +1739,7 @@
           <t>FT-CV-2626</t>
         </is>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="F9" s="16" t="n">
         <v>46311</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1720,7 +1752,7 @@
           <t>U6310-C-620256000</t>
         </is>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="17">
         <f>PARÂMETROS!$C$14*(PARÂMETROS!$F$14/PARÂMETROS!$E$14)*PARÂMETROS!$C$5</f>
         <v/>
       </c>
@@ -1803,7 +1835,7 @@
           <t>FT-CV-2627</t>
         </is>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F10" s="16" t="n">
         <v>46318</v>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1816,7 +1848,7 @@
           <t>U6310-C-620252000</t>
         </is>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="17">
         <f>PARÂMETROS!$C$15*(PARÂMETROS!$F$15/PARÂMETROS!$E$15)*PARÂMETROS!$C$5</f>
         <v/>
       </c>
@@ -1899,7 +1931,7 @@
           <t>FT-CV-2628</t>
         </is>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="16" t="n">
         <v>46325</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1912,7 +1944,7 @@
           <t>U6310-C-620252000</t>
         </is>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="17">
         <f>PARÂMETROS!$C$15*(PARÂMETROS!$F$15/PARÂMETROS!$E$15)*PARÂMETROS!$C$5</f>
         <v/>
       </c>
@@ -1967,17 +1999,6 @@
         <is>
           <t>N/A</t>
         </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="I12" s="15">
-        <f>SUM(I2:I11)</f>
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -2042,7 +2063,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>FT-CV-2619</t>
         </is>
@@ -2055,21 +2076,21 @@
       <c r="C4" s="11" t="n">
         <v>1192.7825</v>
       </c>
-      <c r="D4" s="17">
-        <f>IMPORTAÇÃO!I2</f>
-        <v/>
-      </c>
-      <c r="E4" s="17">
+      <c r="D4" s="19">
+        <f>'IMPORTAÇÃO '!I2</f>
+        <v/>
+      </c>
+      <c r="E4" s="19">
         <f>D4-C4</f>
         <v/>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="20">
         <f>D4/C4-1</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>FT-CV-2620</t>
         </is>
@@ -2082,21 +2103,21 @@
       <c r="C5" s="11" t="n">
         <v>1192.7825</v>
       </c>
-      <c r="D5" s="17">
-        <f>IMPORTAÇÃO!I3</f>
-        <v/>
-      </c>
-      <c r="E5" s="17">
+      <c r="D5" s="19">
+        <f>'IMPORTAÇÃO '!I3</f>
+        <v/>
+      </c>
+      <c r="E5" s="19">
         <f>D5-C5</f>
         <v/>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="20">
         <f>D5/C5-1</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>FT-CV-2621</t>
         </is>
@@ -2109,21 +2130,21 @@
       <c r="C6" s="11" t="n">
         <v>1207.3894</v>
       </c>
-      <c r="D6" s="17">
-        <f>IMPORTAÇÃO!I4</f>
-        <v/>
-      </c>
-      <c r="E6" s="17">
+      <c r="D6" s="19">
+        <f>'IMPORTAÇÃO '!I4</f>
+        <v/>
+      </c>
+      <c r="E6" s="19">
         <f>D6-C6</f>
         <v/>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="20">
         <f>D6/C6-1</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>FT-CV-2622</t>
         </is>
@@ -2136,21 +2157,21 @@
       <c r="C7" s="11" t="n">
         <v>1207.3894</v>
       </c>
-      <c r="D7" s="17">
-        <f>IMPORTAÇÃO!I5</f>
-        <v/>
-      </c>
-      <c r="E7" s="17">
+      <c r="D7" s="19">
+        <f>'IMPORTAÇÃO '!I5</f>
+        <v/>
+      </c>
+      <c r="E7" s="19">
         <f>D7-C7</f>
         <v/>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="20">
         <f>D7/C7-1</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>FT-CV-2623</t>
         </is>
@@ -2163,21 +2184,21 @@
       <c r="C8" s="11" t="n">
         <v>1095.5812</v>
       </c>
-      <c r="D8" s="17">
-        <f>IMPORTAÇÃO!I6</f>
-        <v/>
-      </c>
-      <c r="E8" s="17">
+      <c r="D8" s="19">
+        <f>'IMPORTAÇÃO '!I6</f>
+        <v/>
+      </c>
+      <c r="E8" s="19">
         <f>D8-C8</f>
         <v/>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="20">
         <f>D8/C8-1</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>FT-CV-2624</t>
         </is>
@@ -2190,21 +2211,21 @@
       <c r="C9" s="11" t="n">
         <v>1095.5812</v>
       </c>
-      <c r="D9" s="17">
-        <f>IMPORTAÇÃO!I7</f>
-        <v/>
-      </c>
-      <c r="E9" s="17">
+      <c r="D9" s="19">
+        <f>'IMPORTAÇÃO '!I7</f>
+        <v/>
+      </c>
+      <c r="E9" s="19">
         <f>D9-C9</f>
         <v/>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="20">
         <f>D9/C9-1</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>FT-CV-2625</t>
         </is>
@@ -2217,21 +2238,21 @@
       <c r="C10" s="11" t="n">
         <v>1014.9223</v>
       </c>
-      <c r="D10" s="17">
-        <f>IMPORTAÇÃO!I8</f>
-        <v/>
-      </c>
-      <c r="E10" s="17">
+      <c r="D10" s="19">
+        <f>'IMPORTAÇÃO '!I8</f>
+        <v/>
+      </c>
+      <c r="E10" s="19">
         <f>D10-C10</f>
         <v/>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="20">
         <f>D10/C10-1</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>FT-CV-2626</t>
         </is>
@@ -2244,21 +2265,21 @@
       <c r="C11" s="11" t="n">
         <v>1014.9223</v>
       </c>
-      <c r="D11" s="17">
-        <f>IMPORTAÇÃO!I9</f>
-        <v/>
-      </c>
-      <c r="E11" s="17">
+      <c r="D11" s="19">
+        <f>'IMPORTAÇÃO '!I9</f>
+        <v/>
+      </c>
+      <c r="E11" s="19">
         <f>D11-C11</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="20">
         <f>D11/C11-1</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>FT-CV-2627</t>
         </is>
@@ -2271,21 +2292,21 @@
       <c r="C12" s="11" t="n">
         <v>693.7713999999999</v>
       </c>
-      <c r="D12" s="17">
-        <f>IMPORTAÇÃO!I10</f>
-        <v/>
-      </c>
-      <c r="E12" s="17">
+      <c r="D12" s="19">
+        <f>'IMPORTAÇÃO '!I10</f>
+        <v/>
+      </c>
+      <c r="E12" s="19">
         <f>D12-C12</f>
         <v/>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="20">
         <f>D12/C12-1</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>FT-CV-2628</t>
         </is>
@@ -2298,15 +2319,15 @@
       <c r="C13" s="11" t="n">
         <v>693.7713999999999</v>
       </c>
-      <c r="D13" s="17">
-        <f>IMPORTAÇÃO!I11</f>
-        <v/>
-      </c>
-      <c r="E13" s="17">
+      <c r="D13" s="19">
+        <f>'IMPORTAÇÃO '!I11</f>
+        <v/>
+      </c>
+      <c r="E13" s="19">
         <f>D13-C13</f>
         <v/>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="20">
         <f>D13/C13-1</f>
         <v/>
       </c>
@@ -2317,19 +2338,19 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="14">
         <f>SUM(C4:C13)</f>
         <v/>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="14">
         <f>SUM(D4:D13)</f>
         <v/>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="14">
         <f>D14-C14</f>
         <v/>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="21">
         <f>D14/C14-1</f>
         <v/>
       </c>
